--- a/data/templates/contract_anchor_db/智书合同字段-一般流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-一般流程.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9105" tabRatio="782" firstSheet="2" activeTab="12"/>
+    <workbookView windowHeight="17655" tabRatio="782" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="字段模板" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="199">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -128,6 +128,15 @@
       </rPr>
       <t>（合同执行人）飞书user_id</t>
     </r>
+  </si>
+  <si>
+    <t>合同执行人</t>
+  </si>
+  <si>
+    <t>合同创建人</t>
+  </si>
+  <si>
+    <t>合同创建人user_id</t>
   </si>
   <si>
     <t>custom_15_78cf503c57194e4fb8ad03ded1c4ad60（打印模式）</t>
@@ -1093,7 +1102,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1109,6 +1118,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1444,7 +1459,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1468,16 +1483,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1486,89 +1501,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1583,6 +1598,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1905,13 +1923,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
+  <dimension ref="A1:AK2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="34" width="32" customWidth="1"/>
+    <col min="1" max="37" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58.5" customHeight="1" spans="1:34">
+    <row r="1" ht="58.5" customHeight="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1960,28 +1978,28 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
@@ -1993,7 +2011,7 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
@@ -2002,25 +2020,34 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
-      <c r="S2" s="6"/>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
+      <c r="V2" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 V1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1 Y1"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
@@ -2033,28 +2060,28 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="S2:S1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>DropdownOptions!$A$1:$A$56</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T2:T1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W2:W1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
       <formula1>"增值税专用发票,invoice,普通发票,专用发票"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W2:W1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>DropdownOptions!$C$1:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576">
       <formula1>"对方承担,各自承担,我方承担"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC2:AC1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>DV_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576">
       <formula1>"纸质签约,中国大陆电子签（e签宝）,非中国大陆电子签（Docusign）"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AC1048576">
       <formula1>DropdownOptions!$B$1:$B$20</formula1>
     </dataValidation>
   </dataValidations>
@@ -2067,11 +2094,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="29.716814159292" customWidth="1"/>
-    <col min="7" max="7" width="35.858407079646" customWidth="1"/>
+    <col min="6" max="6" width="29.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="35.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="58.5" customHeight="1" spans="1:7">
@@ -2079,22 +2106,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2107,7 +2134,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="32" customWidth="1"/>
   </cols>
@@ -2117,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2130,7 +2157,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="32" customWidth="1"/>
   </cols>
@@ -2140,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2153,366 +2180,366 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C56"/>
-  <sheetFormatPr defaultColWidth="10.283185840708" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="33.716814159292" customWidth="1"/>
-    <col min="2" max="2" width="17.4247787610619" customWidth="1"/>
-    <col min="3" max="3" width="5.14159292035398" customWidth="1"/>
+    <col min="1" max="1" width="33.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="17.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="5.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2525,529 +2552,529 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T56"/>
-  <sheetFormatPr defaultColWidth="10.283185840708" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1" t="s">
         <v>47</v>
-      </c>
-      <c r="O1" t="s">
-        <v>48</v>
-      </c>
-      <c r="P1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" t="s">
         <v>61</v>
       </c>
-      <c r="O2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P2" t="s">
-        <v>58</v>
-      </c>
       <c r="Q2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" t="s">
         <v>63</v>
       </c>
-      <c r="R2" t="s">
-        <v>64</v>
-      </c>
-      <c r="S2" t="s">
-        <v>60</v>
-      </c>
       <c r="T2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="S3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="F5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="R5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="F6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="F7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="S7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="F8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="S8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="O9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="R9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="S9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="O10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="R10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="O11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="R11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="O12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="S12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="O13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="R13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="S13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="O14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="R14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="S14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="O15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="R15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="S15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="O16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R16" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="S16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="15:19">
       <c r="O17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="S17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="15:19">
       <c r="O18" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="R18" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="S18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="15:19">
       <c r="R19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="S19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="15:19">
       <c r="R20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="15:19">
       <c r="R21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="15:19">
       <c r="R22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="15:19">
       <c r="R23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="15:19">
       <c r="R24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="15:19">
       <c r="R25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="15:19">
       <c r="R26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="15:19">
       <c r="R27" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="15:19">
       <c r="R28" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="15:19">
       <c r="R29" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="15:19">
       <c r="R30" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="15:19">
       <c r="R31" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="15:19">
       <c r="R32" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="18:18">
       <c r="R33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="18:18">
       <c r="R34" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="18:18">
       <c r="R35" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="18:18">
       <c r="R36" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="18:18">
       <c r="R37" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="18:18">
       <c r="R38" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="18:18">
       <c r="R39" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="18:18">
       <c r="R40" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="18:18">
       <c r="R41" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="18:18">
       <c r="R42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="18:18">
       <c r="R43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="18:18">
       <c r="R44" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="18:18">
       <c r="R45" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="18:18">
       <c r="R46" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="18:18">
       <c r="R47" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="18:18">
       <c r="R48" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="18:18">
       <c r="R49" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="18:18">
       <c r="R50" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="18:18">
       <c r="R51" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="18:18">
       <c r="R52" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="18:18">
       <c r="R53" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="18:18">
       <c r="R54" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="18:18">
       <c r="R55" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="18:18">
       <c r="R56" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -3060,10 +3087,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="51.4247787610619" customWidth="1"/>
+    <col min="2" max="2" width="51.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3072,10 +3099,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3088,7 +3115,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="32" customWidth="1"/>
   </cols>
@@ -3098,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3111,7 +3138,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="32" customWidth="1"/>
   </cols>
@@ -3121,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3134,7 +3161,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="11" width="32" customWidth="1"/>
   </cols>
@@ -3144,34 +3171,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3195,7 +3222,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="32" customWidth="1"/>
   </cols>
@@ -3205,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3218,10 +3245,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="32.858407079646" customWidth="1"/>
+    <col min="2" max="2" width="32.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="58.5" customHeight="1" spans="1:2">
@@ -3229,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3242,11 +3269,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="27.858407079646" customWidth="1"/>
-    <col min="9" max="9" width="34.716814159292" customWidth="1"/>
+    <col min="8" max="8" width="27.8571428571429" customWidth="1"/>
+    <col min="9" max="9" width="34.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="58.5" customHeight="1" spans="1:9">
@@ -3254,28 +3281,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates/contract_anchor_db/智书合同字段-一般流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-一般流程.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="200">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>合同创建人user_id</t>
+  </si>
+  <si>
+    <t>申请人状态</t>
   </si>
   <si>
     <t>custom_15_78cf503c57194e4fb8ad03ded1c4ad60（打印模式）</t>
@@ -1923,13 +1926,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="37" width="32" customWidth="1"/>
+    <col min="1" max="38" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58.5" customHeight="1" spans="1:37">
+    <row r="1" ht="58.5" customHeight="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1987,22 +1990,22 @@
       <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
@@ -2020,10 +2023,10 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
@@ -2032,7 +2035,7 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="2" t="s">
@@ -2041,13 +2044,16 @@
       <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:37">
-      <c r="V2" s="7"/>
+      <c r="AL1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38">
+      <c r="W2" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1 Y1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 Z1"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
@@ -2060,28 +2066,28 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="V2:V1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W2:W1048576">
       <formula1>DropdownOptions!$A$1:$A$56</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W2:W1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X2:X1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>"增值税专用发票,invoice,普通发票,专用发票"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA1048576">
       <formula1>DropdownOptions!$C$1:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576">
       <formula1>"对方承担,各自承担,我方承担"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AG2:AG1048576">
       <formula1>DV_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576">
       <formula1>"纸质签约,中国大陆电子签（e签宝）,非中国大陆电子签（Docusign）"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AC1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AD1048576">
       <formula1>DropdownOptions!$B$1:$B$20</formula1>
     </dataValidation>
   </dataValidations>
@@ -2106,22 +2112,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2167,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2189,357 +2195,357 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2556,525 +2562,525 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
+        <v>54</v>
+      </c>
+      <c r="T1" t="s">
         <v>48</v>
-      </c>
-      <c r="M1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" t="s">
         <v>62</v>
       </c>
-      <c r="L2" t="s">
-        <v>63</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="Q2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S2" t="s">
         <v>64</v>
       </c>
-      <c r="O2" t="s">
-        <v>65</v>
-      </c>
-      <c r="P2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>66</v>
-      </c>
-      <c r="R2" t="s">
-        <v>67</v>
-      </c>
-      <c r="S2" t="s">
-        <v>63</v>
-      </c>
       <c r="T2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="F5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="F6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="F7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="F8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="O9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="O10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="O11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="O12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="O13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="O14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="O15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="O16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="15:19">
       <c r="O17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="15:19">
       <c r="O18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="15:19">
       <c r="R19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="15:19">
       <c r="R20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="15:19">
       <c r="R21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="15:19">
       <c r="R22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="15:19">
       <c r="R23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="15:19">
       <c r="R24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="15:19">
       <c r="R25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="15:19">
       <c r="R26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="15:19">
       <c r="R27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="15:19">
       <c r="R28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="15:19">
       <c r="R29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="15:19">
       <c r="R30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="15:19">
       <c r="R31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="15:19">
       <c r="R32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="18:18">
       <c r="R33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="18:18">
       <c r="R34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="18:18">
       <c r="R35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="18:18">
       <c r="R36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="18:18">
       <c r="R37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="18:18">
       <c r="R38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="18:18">
       <c r="R39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="18:18">
       <c r="R40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="18:18">
       <c r="R41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="18:18">
       <c r="R42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="18:18">
       <c r="R43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="18:18">
       <c r="R44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="18:18">
       <c r="R45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="18:18">
       <c r="R46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="18:18">
       <c r="R47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="18:18">
       <c r="R48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="18:18">
       <c r="R49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="18:18">
       <c r="R50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="18:18">
       <c r="R51" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="18:18">
       <c r="R52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="18:18">
       <c r="R53" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="18:18">
       <c r="R54" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="18:18">
       <c r="R55" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="18:18">
       <c r="R56" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3099,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3125,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3148,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3171,34 +3177,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3232,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3256,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3281,28 +3287,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates/contract_anchor_db/智书合同字段-一般流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-一般流程.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="782" firstSheet="2"/>
+    <workbookView windowWidth="26505" windowHeight="17055" tabRatio="782" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="字段模板" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="202">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -69,7 +69,13 @@
     <t>contract_name（合同名称）</t>
   </si>
   <si>
+    <t>合同审批状态</t>
+  </si>
+  <si>
     <t>contractCategory(智书框架合同类型)</t>
+  </si>
+  <si>
+    <t>订单编号</t>
   </si>
   <si>
     <t>pay_type_code（收支类型）</t>
@@ -139,7 +145,7 @@
     <t>合同创建人user_id</t>
   </si>
   <si>
-    <t>申请人状态</t>
+    <t>合同创建人状态</t>
   </si>
   <si>
     <t>custom_15_78cf503c57194e4fb8ad03ded1c4ad60（打印模式）</t>
@@ -1926,41 +1932,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="38" width="32" customWidth="1"/>
+    <col min="1" max="40" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58.5" customHeight="1" spans="1:38">
+    <row r="1" ht="58.5" customHeight="1" spans="1:40">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1981,10 +1987,10 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="6" t="s">
@@ -1993,25 +1999,25 @@
       <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
@@ -2026,68 +2032,74 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:38">
-      <c r="W2" s="7"/>
+      <c r="AM1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
+      <c r="Y2" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 Z1"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1 AB1"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>DV_2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W2:W1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y2:Y1048576">
       <formula1>DropdownOptions!$A$1:$A$56</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X2:X1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>"增值税专用发票,invoice,普通发票,专用发票"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC2:AC1048576">
       <formula1>DropdownOptions!$C$1:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576">
       <formula1>"对方承担,各自承担,我方承担"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AG2:AG1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AI2:AI1048576">
       <formula1>DV_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ1048576">
       <formula1>"纸质签约,中国大陆电子签（e签宝）,非中国大陆电子签（Docusign）"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AD1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AD2:AF1048576">
       <formula1>DropdownOptions!$B$1:$B$20</formula1>
     </dataValidation>
   </dataValidations>
@@ -2112,22 +2124,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2150,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2195,357 +2207,357 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2562,525 +2574,525 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T1" t="s">
         <v>50</v>
-      </c>
-      <c r="N1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" t="s">
         <v>64</v>
       </c>
-      <c r="N2" t="s">
-        <v>65</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R2" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" t="s">
         <v>66</v>
       </c>
-      <c r="P2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>67</v>
-      </c>
-      <c r="R2" t="s">
-        <v>68</v>
-      </c>
-      <c r="S2" t="s">
-        <v>64</v>
-      </c>
       <c r="T2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="F5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="S5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="T5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="F6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="S6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="F7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="S7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="F8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="O9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="O10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="R10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="S10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="O11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="S11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="O12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="O13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="R13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="S13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="O14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="S14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="O15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="O16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="R16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="S16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="15:19">
       <c r="O17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R17" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="S17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="15:19">
       <c r="O18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="15:19">
       <c r="R19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="S19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="15:19">
       <c r="R20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="S20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="15:19">
       <c r="R21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="15:19">
       <c r="R22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="15:19">
       <c r="R23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="15:19">
       <c r="R24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="15:19">
       <c r="R25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="15:19">
       <c r="R26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="15:19">
       <c r="R27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="15:19">
       <c r="R28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="15:19">
       <c r="R29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="15:19">
       <c r="R30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="15:19">
       <c r="R31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="15:19">
       <c r="R32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="18:18">
       <c r="R33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="18:18">
       <c r="R34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="18:18">
       <c r="R35" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="18:18">
       <c r="R36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="18:18">
       <c r="R37" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="18:18">
       <c r="R38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="18:18">
       <c r="R39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="18:18">
       <c r="R40" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="18:18">
       <c r="R41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="18:18">
       <c r="R42" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="18:18">
       <c r="R43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="18:18">
       <c r="R44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="18:18">
       <c r="R45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="18:18">
       <c r="R46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="18:18">
       <c r="R47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="18:18">
       <c r="R48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="18:18">
       <c r="R49" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="18:18">
       <c r="R50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="18:18">
       <c r="R51" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="18:18">
       <c r="R52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="18:18">
       <c r="R53" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="18:18">
       <c r="R54" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="18:18">
       <c r="R55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="18:18">
       <c r="R56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3105,10 +3117,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3131,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3154,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3177,34 +3189,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3238,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3262,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3287,28 +3299,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
